--- a/resultados.xlsx
+++ b/resultados.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jfbal\Downloads\Projecto2_Alpha4LinhaV3.0\Projecto2_Alpha4'\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jfbal\Documents\Projecto2_Alpha4'\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D50092A5-F46C-4E96-BCB7-0047F7D1C1BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EC0DDCD-6CD4-408E-AE34-DF35A9CEF0DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{5C53708D-411B-488D-801D-AFAFD207A61B}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>Comparação</t>
   </si>
@@ -90,6 +90,9 @@
   </si>
   <si>
     <t>Humano vs IA (Opcional)</t>
+  </si>
+  <si>
+    <t>O Minimax joga para ganhar e reage ao adversário. O Aleatório joga às cegas, não aproveitando oportunidades nem bloqueando o Minimax, o que explica a taxa de vitórias de 100%.</t>
   </si>
 </sst>
 </file>
@@ -125,8 +128,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -469,12 +479,12 @@
     <col min="3" max="3" width="15.88671875" customWidth="1"/>
     <col min="4" max="4" width="15.77734375" customWidth="1"/>
     <col min="5" max="5" width="7.88671875" customWidth="1"/>
-    <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="22.5546875" customWidth="1"/>
+    <col min="6" max="6" width="21" customWidth="1"/>
+    <col min="7" max="7" width="21.88671875" customWidth="1"/>
     <col min="8" max="8" width="20.21875" customWidth="1"/>
     <col min="9" max="9" width="15.5546875" customWidth="1"/>
     <col min="10" max="10" width="14.77734375" customWidth="1"/>
-    <col min="11" max="11" width="35.109375" customWidth="1"/>
+    <col min="11" max="11" width="143.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
@@ -516,11 +526,42 @@
       <c r="A2" t="s">
         <v>11</v>
       </c>
+      <c r="B2" s="1">
+        <v>50</v>
+      </c>
+      <c r="C2" s="1">
+        <v>50</v>
+      </c>
+      <c r="D2" s="1">
+        <v>0</v>
+      </c>
+      <c r="E2" s="1">
+        <v>0</v>
+      </c>
+      <c r="F2" s="2">
+        <v>1</v>
+      </c>
+      <c r="G2" s="2">
+        <v>0</v>
+      </c>
+      <c r="H2" s="1">
+        <v>0.19689999999999999</v>
+      </c>
+      <c r="I2" s="1">
+        <v>0.44500000000000001</v>
+      </c>
+      <c r="J2" s="1">
+        <v>0.11799999999999999</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>12</v>
       </c>
+      <c r="B3" s="3"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
@@ -544,5 +585,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/resultados.xlsx
+++ b/resultados.xlsx
@@ -1,41 +1,188 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jfbal\Documents\Projecto2_Alpha4'\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15BBA085-033F-4EC5-8918-218BAAE3E6C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Folha1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="52">
+  <si>
+    <t>Comparação</t>
+  </si>
+  <si>
+    <t>Nº de Jogos</t>
+  </si>
+  <si>
+    <t>Vitórias Jogador 1</t>
+  </si>
+  <si>
+    <t>Vitórias Jogador 2</t>
+  </si>
+  <si>
+    <t>Empates</t>
+  </si>
+  <si>
+    <t>Taxa de Vitórias Jogador 1</t>
+  </si>
+  <si>
+    <t>Taxa de Vitórias Jogador 2</t>
+  </si>
+  <si>
+    <t>Duração Média do Jogo</t>
+  </si>
+  <si>
+    <t>Duração Máxima</t>
+  </si>
+  <si>
+    <t>Duração Mínima</t>
+  </si>
+  <si>
+    <t>Diferenças de Comportamento Observado</t>
+  </si>
+  <si>
+    <t>MiniMax vs Aleatório</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>100.00%</t>
+  </si>
+  <si>
+    <t>0.00%</t>
+  </si>
+  <si>
+    <t>0.1969</t>
+  </si>
+  <si>
+    <t>0.445</t>
+  </si>
+  <si>
+    <t>0.118</t>
+  </si>
+  <si>
+    <t>O Minimax joga para ganhar e reage ao adversário. O Aleatório joga às cegas, não aproveitando oportunidades nem bloqueando o Minimax, o que explica a taxa de vitórias de 100%.</t>
+  </si>
+  <si>
+    <t>MCTS vs Aleatório</t>
+  </si>
+  <si>
+    <t>2.7666</t>
+  </si>
+  <si>
+    <t>4.8070</t>
+  </si>
+  <si>
+    <t>2.0550</t>
+  </si>
+  <si>
+    <t>O MCTS, com 1000 iterações, supera claramente o jogador aleatório . O MCTS é muito superior a jogadas puramente aleatórias. Sendo que a duração média  é também bastante superior à do Minimax.</t>
+  </si>
+  <si>
+    <t>1º comb MiniMax vs MCTS</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>86.00%</t>
+  </si>
+  <si>
+    <t>14.00%</t>
+  </si>
+  <si>
+    <t>1.0251</t>
+  </si>
+  <si>
+    <t>1.6190</t>
+  </si>
+  <si>
+    <t>0.4330</t>
+  </si>
+  <si>
+    <t>Com poucas iterações o MCTS não explora a árvore suficientemente e os rollouts aleatórios no Connect 4 são pouco informativos. O Minimax, mesmo com pouca profundidade, beneficia da função heurística com conhecimento do domínio. Duração média/baixa pois ambos os algoritmos usam configurações leves.</t>
+  </si>
+  <si>
+    <t>2º comb MiniMax vs MCTS</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>88.00%</t>
+  </si>
+  <si>
+    <t>12.00%</t>
+  </si>
+  <si>
+    <t>7.1903</t>
+  </si>
+  <si>
+    <t>11.9040</t>
+  </si>
+  <si>
+    <t>2.6710</t>
+  </si>
+  <si>
+    <t>Resultados bastante semelhantes 1ª combinação apesar das 1500 iterações do MCTS. Sendo que há um aumento brusco de duração de cada jogo.</t>
+  </si>
+  <si>
+    <t>3º comb MiniMax vs MCTS</t>
+  </si>
+  <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>98.00%</t>
+  </si>
+  <si>
+    <t>18.1609</t>
+  </si>
+  <si>
+    <t>63.1460</t>
+  </si>
+  <si>
+    <t>10.8440</t>
+  </si>
+  <si>
+    <t>A duração média dispara para 18s , tornando-se a mais pesada computacionalmente.</t>
+  </si>
+  <si>
+    <t>Humano vs IA (Opcional)</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -64,14 +211,31 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,227 +560,403 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AL7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="23.8984375" customWidth="1"/>
+    <col min="2" max="2" width="10.69921875" customWidth="1"/>
+    <col min="3" max="3" width="15.796875" customWidth="1"/>
+    <col min="4" max="4" width="16.5" customWidth="1"/>
+    <col min="6" max="6" width="22.796875" customWidth="1"/>
+    <col min="7" max="7" width="22.8984375" customWidth="1"/>
+    <col min="8" max="8" width="20.3984375" customWidth="1"/>
+    <col min="9" max="9" width="16" customWidth="1"/>
+    <col min="10" max="10" width="14.8984375" customWidth="1"/>
+    <col min="11" max="11" width="36.5" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Comparação</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Nº de Jogos</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Vitórias Jogador 1</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Vitórias Jogador 2</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Empates</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Taxa de Vitórias Jogador 1</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Taxa de Vitórias Jogador 2</v>
-      </c>
-      <c r="H1" t="str">
-        <v>Duração Média do Jogo</v>
-      </c>
-      <c r="I1" t="str">
-        <v>Duração Máxima</v>
-      </c>
-      <c r="J1" t="str">
-        <v>Duração Mínima</v>
-      </c>
-      <c r="K1" t="str">
-        <v>Diferenças de Comportamento Observado</v>
-      </c>
+    <row r="1" spans="1:38" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+      <c r="T1" s="1"/>
+      <c r="U1" s="1"/>
+      <c r="V1" s="1"/>
+      <c r="W1" s="1"/>
+      <c r="X1" s="1"/>
+      <c r="Y1" s="1"/>
+      <c r="Z1" s="1"/>
+      <c r="AA1" s="1"/>
+      <c r="AB1" s="1"/>
+      <c r="AC1" s="1"/>
+      <c r="AD1" s="1"/>
+      <c r="AE1" s="1"/>
+      <c r="AF1" s="1"/>
+      <c r="AG1" s="1"/>
+      <c r="AH1" s="1"/>
+      <c r="AI1" s="1"/>
+      <c r="AJ1" s="1"/>
+      <c r="AK1" s="1"/>
+      <c r="AL1" s="1"/>
     </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>MiniMax vs Aleatório</v>
-      </c>
-      <c r="B2" t="str">
+    <row r="2" spans="1:38" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
+      <c r="U2" s="1"/>
+      <c r="V2" s="1"/>
+      <c r="W2" s="1"/>
+      <c r="X2" s="1"/>
+      <c r="Y2" s="1"/>
+      <c r="Z2" s="1"/>
+      <c r="AA2" s="1"/>
+      <c r="AB2" s="1"/>
+      <c r="AC2" s="1"/>
+      <c r="AD2" s="1"/>
+      <c r="AE2" s="1"/>
+      <c r="AF2" s="1"/>
+      <c r="AG2" s="1"/>
+      <c r="AH2" s="1"/>
+      <c r="AI2" s="1"/>
+      <c r="AJ2" s="1"/>
+      <c r="AK2" s="1"/>
+      <c r="AL2" s="1"/>
+    </row>
+    <row r="3" spans="1:38" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
+      <c r="N3" s="1"/>
+      <c r="O3" s="1"/>
+      <c r="P3" s="1"/>
+      <c r="Q3" s="1"/>
+      <c r="R3" s="1"/>
+      <c r="S3" s="1"/>
+      <c r="T3" s="1"/>
+      <c r="U3" s="1"/>
+      <c r="V3" s="1"/>
+      <c r="W3" s="1"/>
+      <c r="X3" s="1"/>
+      <c r="Y3" s="1"/>
+      <c r="Z3" s="1"/>
+      <c r="AA3" s="1"/>
+      <c r="AB3" s="1"/>
+      <c r="AC3" s="1"/>
+      <c r="AD3" s="1"/>
+      <c r="AE3" s="1"/>
+      <c r="AF3" s="1"/>
+      <c r="AG3" s="1"/>
+      <c r="AH3" s="1"/>
+      <c r="AI3" s="1"/>
+      <c r="AJ3" s="1"/>
+      <c r="AK3" s="1"/>
+      <c r="AL3" s="1"/>
+    </row>
+    <row r="4" spans="1:38" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="1"/>
+      <c r="O4" s="1"/>
+      <c r="P4" s="1"/>
+      <c r="Q4" s="1"/>
+      <c r="R4" s="1"/>
+      <c r="S4" s="1"/>
+      <c r="T4" s="1"/>
+      <c r="U4" s="1"/>
+      <c r="V4" s="1"/>
+      <c r="W4" s="1"/>
+      <c r="X4" s="1"/>
+      <c r="Y4" s="1"/>
+      <c r="Z4" s="1"/>
+      <c r="AA4" s="1"/>
+      <c r="AB4" s="1"/>
+      <c r="AC4" s="1"/>
+      <c r="AD4" s="1"/>
+      <c r="AE4" s="1"/>
+      <c r="AF4" s="1"/>
+      <c r="AG4" s="1"/>
+      <c r="AH4" s="1"/>
+      <c r="AI4" s="1"/>
+      <c r="AJ4" s="1"/>
+      <c r="AK4" s="1"/>
+      <c r="AL4" s="1"/>
+    </row>
+    <row r="5" spans="1:38" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="1"/>
+      <c r="O5" s="1"/>
+      <c r="P5" s="1"/>
+      <c r="Q5" s="1"/>
+      <c r="R5" s="1"/>
+      <c r="S5" s="1"/>
+      <c r="T5" s="1"/>
+      <c r="U5" s="1"/>
+      <c r="V5" s="1"/>
+      <c r="W5" s="1"/>
+      <c r="X5" s="1"/>
+      <c r="Y5" s="1"/>
+      <c r="Z5" s="1"/>
+      <c r="AA5" s="1"/>
+      <c r="AB5" s="1"/>
+      <c r="AC5" s="1"/>
+      <c r="AD5" s="1"/>
+      <c r="AE5" s="1"/>
+      <c r="AF5" s="1"/>
+      <c r="AG5" s="1"/>
+      <c r="AH5" s="1"/>
+      <c r="AI5" s="1"/>
+      <c r="AJ5" s="1"/>
+      <c r="AK5" s="1"/>
+      <c r="AL5" s="1"/>
+    </row>
+    <row r="6" spans="1:38" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="K6" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C2" t="str">
-        <v>50</v>
-      </c>
-      <c r="D2" t="str">
-        <v>0</v>
-      </c>
-      <c r="E2" t="str">
-        <v>0</v>
-      </c>
-      <c r="F2" t="str">
-        <v>100.00%</v>
-      </c>
-      <c r="G2" t="str">
-        <v>0.00%</v>
-      </c>
-      <c r="H2" t="str">
-        <v>0.1969</v>
-      </c>
-      <c r="I2" t="str">
-        <v>0.445</v>
-      </c>
-      <c r="J2" t="str">
-        <v>0.118</v>
-      </c>
-      <c r="K2" t="str">
-        <v>O Minimax joga para ganhar e reage ao adversário. O Aleatório joga às cegas, não aproveitando oportunidades nem bloqueando o Minimax, o que explica a taxa de vitórias de 100%.</v>
-      </c>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
+      <c r="P6" s="1"/>
+      <c r="Q6" s="1"/>
+      <c r="R6" s="1"/>
+      <c r="S6" s="1"/>
+      <c r="T6" s="1"/>
+      <c r="U6" s="1"/>
+      <c r="V6" s="1"/>
+      <c r="W6" s="1"/>
+      <c r="X6" s="1"/>
+      <c r="Y6" s="1"/>
+      <c r="Z6" s="1"/>
+      <c r="AA6" s="1"/>
+      <c r="AB6" s="1"/>
+      <c r="AC6" s="1"/>
+      <c r="AD6" s="1"/>
+      <c r="AE6" s="1"/>
+      <c r="AF6" s="1"/>
+      <c r="AG6" s="1"/>
+      <c r="AH6" s="1"/>
+      <c r="AI6" s="1"/>
+      <c r="AJ6" s="1"/>
+      <c r="AK6" s="1"/>
+      <c r="AL6" s="1"/>
     </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>MCTS vs Aleatório</v>
-      </c>
-      <c r="B3" t="str">
-        <v>50</v>
-      </c>
-      <c r="C3" t="str">
-        <v>50</v>
-      </c>
-      <c r="D3" t="str">
-        <v>0</v>
-      </c>
-      <c r="E3" t="str">
-        <v>0</v>
-      </c>
-      <c r="F3" t="str">
-        <v>100.00%</v>
-      </c>
-      <c r="G3" t="str">
-        <v>0.00%</v>
-      </c>
-      <c r="H3" t="str">
-        <v>2.7666</v>
-      </c>
-      <c r="I3" t="str">
-        <v>4.8070</v>
-      </c>
-      <c r="J3" t="str">
-        <v>2.0550</v>
-      </c>
-      <c r="K3" t="str">
-        <v>O MCTS, com 1000 iterações, supera claramente o jogador aleatório . O MCTS é muito superior a jogadas puramente aleatórias. Sendo que a duração média  é também bastante superior à do Minimax.</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>1º comb MiniMax vs MCTS</v>
-      </c>
-      <c r="B4" t="str">
-        <v>50</v>
-      </c>
-      <c r="C4" t="str">
-        <v>43</v>
-      </c>
-      <c r="D4" t="str">
-        <v>7</v>
-      </c>
-      <c r="E4" t="str">
-        <v>0</v>
-      </c>
-      <c r="F4" t="str">
-        <v>86.00%</v>
-      </c>
-      <c r="G4" t="str">
-        <v>14.00%</v>
-      </c>
-      <c r="H4" t="str">
-        <v>1.0251</v>
-      </c>
-      <c r="I4" t="str">
-        <v>1.6190</v>
-      </c>
-      <c r="J4" t="str">
-        <v>0.4330</v>
-      </c>
-      <c r="K4" t="str">
-        <v>Com poucas iterações o MCTS não explora a árvore suficientemente e os rollouts aleatórios no Connect 4 são pouco informativos. O Minimax, mesmo com pouca profundidade, beneficia da função heurística com conhecimento do domínio. Duração média/baixa pois ambos os algoritmos usam configurações leves.</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>2º comb MiniMax vs MCTS</v>
-      </c>
-      <c r="B5" t="str">
-        <v>50</v>
-      </c>
-      <c r="C5" t="str">
-        <v>44</v>
-      </c>
-      <c r="D5" t="str">
-        <v>6</v>
-      </c>
-      <c r="E5" t="str">
-        <v>0</v>
-      </c>
-      <c r="F5" t="str">
-        <v>88.00%</v>
-      </c>
-      <c r="G5" t="str">
-        <v>12.00%</v>
-      </c>
-      <c r="H5" t="str">
-        <v>7.1903</v>
-      </c>
-      <c r="I5" t="str">
-        <v>11.9040</v>
-      </c>
-      <c r="J5" t="str">
-        <v>2.6710</v>
-      </c>
-      <c r="K5" t="str">
-        <v>Resultados bastante semelhantes 1ª combinação apesar das 1500 iterações do MCTS. Sendo que há um aumento brusco de duração de cada jogo.</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>3º comb MiniMax vs MCTS</v>
-      </c>
-      <c r="B6" t="str">
-        <v>50</v>
-      </c>
-      <c r="C6" t="str">
-        <v>49</v>
-      </c>
-      <c r="D6" t="str">
-        <v>0</v>
-      </c>
-      <c r="E6" t="str">
-        <v>1</v>
-      </c>
-      <c r="F6" t="str">
-        <v>98.00%</v>
-      </c>
-      <c r="G6" t="str">
-        <v>0.00%</v>
-      </c>
-      <c r="H6" t="str">
-        <v>18.1609</v>
-      </c>
-      <c r="I6" t="str">
-        <v>63.1460</v>
-      </c>
-      <c r="J6" t="str">
-        <v>10.8440</v>
-      </c>
-      <c r="K6" t="str">
-        <v>A duração média dispara para 18s , tornando-se a mais pesada computacionalmente.</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>Humano vs IA (Opcional)</v>
+    <row r="7" spans="1:38" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K7"/>
+    <ignoredError sqref="A1:K7" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/resultados.xlsx
+++ b/resultados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jfbal\Documents\Projecto2_Alpha4'\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15BBA085-033F-4EC5-8918-218BAAE3E6C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{949391AF-69C6-4BBB-9AF1-B6D24ECF374C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -182,8 +182,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -219,9 +227,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -562,7 +568,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AL7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="23.8984375" customWidth="1"/>
     <col min="2" max="2" width="10.69921875" customWidth="1"/>
@@ -576,7 +582,7 @@
     <col min="11" max="11" width="36.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -638,7 +644,7 @@
       <c r="AK1" s="1"/>
       <c r="AL1" s="1"/>
     </row>
-    <row r="2" spans="1:38" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
@@ -700,7 +706,7 @@
       <c r="AK2" s="1"/>
       <c r="AL2" s="1"/>
     </row>
-    <row r="3" spans="1:38" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>20</v>
       </c>
@@ -762,7 +768,7 @@
       <c r="AK3" s="1"/>
       <c r="AL3" s="1"/>
     </row>
-    <row r="4" spans="1:38" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>25</v>
       </c>
@@ -824,7 +830,7 @@
       <c r="AK4" s="1"/>
       <c r="AL4" s="1"/>
     </row>
-    <row r="5" spans="1:38" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>34</v>
       </c>
@@ -886,7 +892,7 @@
       <c r="AK5" s="1"/>
       <c r="AL5" s="1"/>
     </row>
-    <row r="6" spans="1:38" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>43</v>
       </c>
@@ -917,7 +923,7 @@
       <c r="J6" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="K6" s="3" t="s">
+      <c r="K6" s="2" t="s">
         <v>50</v>
       </c>
       <c r="L6" s="1"/>
@@ -948,15 +954,16 @@
       <c r="AK6" s="1"/>
       <c r="AL6" s="1"/>
     </row>
-    <row r="7" spans="1:38" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>51</v>
       </c>
+      <c r="B7" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:K7" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:K6 A7 C7 E7:K7" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>